--- a/app/templates/report/dashboard.checkin.xlsx
+++ b/app/templates/report/dashboard.checkin.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\Development\projects\ciber\cotown\back\app\templates\report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Data\Development\projects\oimbra\custom\cotown\back\app\templates\report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75AF9A93-958F-400D-9F92-274778FB9E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{565141AE-BCBE-4E08-AFBA-D9C0AF83FC6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" tabRatio="750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Entradas" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Entradas!$A$2:$AH$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Entradas!$A$2:$AI$2</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
   <si>
     <t>Check-in</t>
   </si>
@@ -138,6 +138,9 @@
   </si>
   <si>
     <t>Entradas</t>
+  </si>
+  <si>
+    <t>Check-in requerido</t>
   </si>
 </sst>
 </file>
@@ -677,27 +680,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="24.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AI3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="24.85546875" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="9" width="11.44140625" style="1" customWidth="1"/>
-    <col min="10" max="11" width="9.109375" style="11" customWidth="1"/>
-    <col min="12" max="12" width="7.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="25" width="13.109375" style="1" customWidth="1"/>
-    <col min="26" max="26" width="50.77734375" style="1" customWidth="1"/>
-    <col min="27" max="28" width="10.44140625" style="1" customWidth="1"/>
-    <col min="29" max="29" width="64.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="19.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="26.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="35.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="18.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="24.88671875" style="1"/>
+    <col min="1" max="1" width="6.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="9" width="11.42578125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="9.140625" style="11" customWidth="1"/>
+    <col min="12" max="12" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="26" width="13.140625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="50.7109375" style="1" customWidth="1"/>
+    <col min="28" max="29" width="10.42578125" style="1" customWidth="1"/>
+    <col min="30" max="30" width="64.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="19.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="26.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="35.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="18.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="24.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>36</v>
       </c>
@@ -718,24 +721,24 @@
       <c r="N1" s="8"/>
       <c r="O1" s="8"/>
       <c r="P1" s="8"/>
-      <c r="Q1" s="8" t="s">
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="R1" s="8"/>
       <c r="S1" s="8"/>
-      <c r="T1" s="8" t="s">
+      <c r="T1" s="8"/>
+      <c r="U1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="U1" s="8"/>
-      <c r="V1" s="8" t="s">
+      <c r="V1" s="8"/>
+      <c r="W1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="W1" s="8"/>
-      <c r="X1" s="8" t="s">
+      <c r="X1" s="8"/>
+      <c r="Y1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="Y1" s="8"/>
-      <c r="Z1" s="3"/>
+      <c r="Z1" s="8"/>
       <c r="AA1" s="3"/>
       <c r="AB1" s="3"/>
       <c r="AC1" s="3"/>
@@ -744,8 +747,9 @@
       <c r="AF1" s="3"/>
       <c r="AG1" s="3"/>
       <c r="AH1" s="3"/>
+      <c r="AI1" s="3"/>
     </row>
-    <row r="2" spans="1:34" s="4" customFormat="1" ht="37.799999999999997" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" s="4" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>5</v>
       </c>
@@ -789,67 +793,70 @@
         <v>18</v>
       </c>
       <c r="O2" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="P2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="Q2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="R2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="S2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="S2" s="6" t="s">
+      <c r="T2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="T2" s="6" t="s">
+      <c r="U2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="U2" s="6" t="s">
+      <c r="V2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="V2" s="6" t="s">
+      <c r="W2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="W2" s="6" t="s">
+      <c r="X2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="X2" s="6" t="s">
+      <c r="Y2" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="Y2" s="6" t="s">
+      <c r="Z2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="Z2" s="6" t="s">
+      <c r="AA2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AA2" s="6" t="s">
+      <c r="AB2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AB2" s="6" t="s">
+      <c r="AC2" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="AC2" s="6" t="s">
+      <c r="AD2" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="AD2" s="6" t="s">
+      <c r="AE2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="AE2" s="6" t="s">
+      <c r="AF2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AF2" s="6" t="s">
+      <c r="AG2" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="AG2" s="6" t="s">
+      <c r="AH2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="AH2" s="6" t="s">
+      <c r="AI2" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:34" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="10" t="s">
@@ -898,9 +905,10 @@
       <c r="AF3" s="2"/>
       <c r="AG3" s="2"/>
       <c r="AH3" s="2"/>
+      <c r="AI3" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AH2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:AI2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
